--- a/artfynd/A 29888-2024 artfynd.xlsx
+++ b/artfynd/A 29888-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119495712</v>
+        <v>119495715</v>
       </c>
       <c r="B2" t="n">
-        <v>78326</v>
+        <v>74450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>924</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119495715</v>
+        <v>119495712</v>
       </c>
       <c r="B4" t="n">
-        <v>74450</v>
+        <v>78326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>924</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
